--- a/data/trans_orig/IMC_inf_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43124</t>
+          <t>43012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>25399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29329</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89923</t>
+          <t>88887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114520</t>
+          <t>113642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>91606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115532</t>
+          <t>115245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190345</t>
+          <t>190153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222327</t>
+          <t>223668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116882</t>
+          <t>117760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141479</t>
+          <t>142515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113637</t>
+          <t>113924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136899</t>
+          <t>137563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238244</t>
+          <t>236903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270226</t>
+          <t>270418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43923</t>
+          <t>42584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>58848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76459</t>
+          <t>77642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107533</t>
+          <t>105805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132136</t>
+          <t>132723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80518</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56604</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74847</t>
+          <t>74215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125367</t>
+          <t>124780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149970</t>
+          <t>151698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42778</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72837</t>
+          <t>72408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95472</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103335</t>
+          <t>103745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132014</t>
+          <t>132261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148016</t>
+          <t>148756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165878</t>
+          <t>166818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106732</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129367</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260984</t>
+          <t>260737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289663</t>
+          <t>289253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187155</t>
+          <t>186354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221822</t>
+          <t>221172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255946</t>
+          <t>253811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>293625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>452143</t>
+          <t>450305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506013</t>
+          <t>505438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>356250</t>
+          <t>356900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>390917</t>
+          <t>391718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>311828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>351642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>677512</t>
+          <t>678087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>731382</t>
+          <t>733220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22723</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>34465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36945</t>
+          <t>37376</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80182</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103800</t>
+          <t>105237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124794</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149365</t>
+          <t>150561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>211236</t>
+          <t>213274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246020</t>
+          <t>249113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96108</t>
+          <t>94671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>75638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101405</t>
+          <t>101393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180088</t>
+          <t>176995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>214872</t>
+          <t>212834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81658</t>
+          <t>82507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59606</t>
+          <t>60430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80007</t>
+          <t>78874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126633</t>
+          <t>127570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154399</t>
+          <t>154877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>55127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74891</t>
+          <t>74690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60655</t>
+          <t>61788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81056</t>
+          <t>80232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123897</t>
+          <t>123419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151663</t>
+          <t>150726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51323</t>
+          <t>51565</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>50806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71473</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>89685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118033</t>
+          <t>117632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106151</t>
+          <t>105909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123810</t>
+          <t>124559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>91505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111268</t>
+          <t>111289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201536</t>
+          <t>201937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229660</t>
+          <t>229884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201556</t>
+          <t>204318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239622</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260698</t>
+          <t>262113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>300282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>475219</t>
+          <t>474635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>527639</t>
+          <t>526569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287408</t>
+          <t>284693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325474</t>
+          <t>322712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257924</t>
+          <t>256329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295913</t>
+          <t>294498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>556002</t>
+          <t>557072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>608422</t>
+          <t>609006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37928</t>
+          <t>37509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>22793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27532</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40253</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63552</t>
+          <t>62613</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>84950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>99249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123426</t>
+          <t>123313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170081</t>
+          <t>170110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202545</t>
+          <t>202651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99560</t>
+          <t>99670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121068</t>
+          <t>122007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102831</t>
+          <t>102944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127260</t>
+          <t>127008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208332</t>
+          <t>208226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240796</t>
+          <t>240767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56143</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77354</t>
+          <t>77421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75489</t>
+          <t>75619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97457</t>
+          <t>97800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138294</t>
+          <t>137995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167735</t>
+          <t>168035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93499</t>
+          <t>93432</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114710</t>
+          <t>115084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74423</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96391</t>
+          <t>96261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174998</t>
+          <t>174698</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204439</t>
+          <t>204738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>42354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39690</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>58784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68881</t>
+          <t>67341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94937</t>
+          <t>93782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112776</t>
+          <t>112910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129613</t>
+          <t>130617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94932</t>
+          <t>95219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114313</t>
+          <t>114753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214329</t>
+          <t>215484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240385</t>
+          <t>241925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170642</t>
+          <t>170586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208172</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>241033</t>
+          <t>241538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>280406</t>
+          <t>281183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>425364</t>
+          <t>422726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>481685</t>
+          <t>477154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336230</t>
+          <t>336319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>373760</t>
+          <t>373816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>303528</t>
+          <t>302751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>342396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>646651</t>
+          <t>651182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702972</t>
+          <t>705610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63796</t>
+          <t>64067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>68781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90629</t>
+          <t>90662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>120847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148157</t>
+          <t>147842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74975</t>
+          <t>74704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94191</t>
+          <t>93198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78993</t>
+          <t>78960</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100581</t>
+          <t>100841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160236</t>
+          <t>160551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188676</t>
+          <t>187546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47135</t>
+          <t>47755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69828</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65326</t>
+          <t>64378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90881</t>
+          <t>89225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119712</t>
+          <t>120175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153426</t>
+          <t>153888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92660</t>
+          <t>92568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115353</t>
+          <t>114733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94743</t>
+          <t>96399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120298</t>
+          <t>121246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194686</t>
+          <t>194224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228400</t>
+          <t>227937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55888</t>
+          <t>55375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71240</t>
+          <t>70745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109332</t>
+          <t>108911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108258</t>
+          <t>107207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158086</t>
+          <t>157984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192648</t>
+          <t>193161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219560</t>
+          <t>221102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168773</t>
+          <t>169194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206865</t>
+          <t>207360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>368556</t>
+          <t>368658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>418384</t>
+          <t>419435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138492</t>
+          <t>136345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185800</t>
+          <t>185752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229878</t>
+          <t>228801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>282178</t>
+          <t>279715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380194</t>
+          <t>379725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453554</t>
+          <t>453220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389570</t>
+          <t>389618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436878</t>
+          <t>439025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370674</t>
+          <t>373137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422974</t>
+          <t>424051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774668</t>
+          <t>775002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>848028</t>
+          <t>848497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R2-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20551</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15469</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25623</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15716</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11691</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20363</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11715</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20272</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20551</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15618</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25444</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43012</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20466</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15394</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25548</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15719</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11072</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19744</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11163</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19720</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20466</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15573</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25399</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>43364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41017</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>41017</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41017</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31435</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31435</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31435</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>41017</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>41017</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>41017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>103269</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90440</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>115313</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>102632</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>88887</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>113642</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>90376</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>115494</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>44,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>103269</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>91606</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>115245</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190153</t>
+          <t>189029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223668</t>
+          <t>221052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125900</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>113856</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>138729</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>128770</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>117760</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142515</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>115908</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>141026</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>55,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>125900</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>113924</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>137563</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>54,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236903</t>
+          <t>239519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>270418</t>
+          <t>271542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>229169</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>229169</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>229169</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>231402</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>231402</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>231402</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>229169</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>229169</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>229169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>67217</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58282</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77049</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52162</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42584</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>61749</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43811</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62034</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>67217</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58848</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>77642</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105805</t>
+          <t>106491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132723</t>
+          <t>132239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65846</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56014</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74781</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72279</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62692</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81857</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62407</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>80630</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65846</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55421</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74215</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124780</t>
+          <t>125264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151698</t>
+          <t>151012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>133063</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133063</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133063</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>124441</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>124441</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>124441</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>133063</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>133063</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>133063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>83953</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>72916</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96158</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>33215</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42038</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>25289</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>41840</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>83953</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>72408</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>94866</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103745</t>
+          <t>102052</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132261</t>
+          <t>131362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118251</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>106046</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>129288</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>157579</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>148756</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166818</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>148954</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>165505</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>118251</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>107338</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>129796</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260737</t>
+          <t>261636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289253</t>
+          <t>290946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202204</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202204</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202204</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190794</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190794</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190794</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202204</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202204</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>255865</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>293526</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>186354</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>221172</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>186635</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>223096</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>253811</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>293625</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450305</t>
+          <t>450692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505438</t>
+          <t>504253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>330463</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>311927</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>349588</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>374348</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>356900</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>391718</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>354976</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>391437</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>330463</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>311828</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>351642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>678087</t>
+          <t>679272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>733220</t>
+          <t>732833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>605453</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>863</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>578072</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>578072</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>578072</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>605453</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12868</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17352</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15924</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11505</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19854</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11513</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20636</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12868</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8747</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17420</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>34489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14786</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19128</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16090</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12160</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20509</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11378</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20501</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14786</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10234</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18907</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>53,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>36927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27654</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27654</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27654</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32014</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32014</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32014</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27654</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27654</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>137547</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>123364</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>148974</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>60,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>54,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>65,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91853</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>80529</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>105237</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>80803</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>104427</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>45,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>137547</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>124806</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>150561</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>60,81%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>213274</t>
+          <t>212560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249113</t>
+          <t>246050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>77225</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>102835</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>45,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>108055</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>94671</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>119379</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95481</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>119105</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>54,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88652</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>75638</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>101393</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>39,19%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176995</t>
+          <t>180058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212834</t>
+          <t>213548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>226199</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>226199</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>226199</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>199908</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>226199</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>226199</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>226199</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69383</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59927</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79240</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>72140</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62944</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>82507</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61037</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>81347</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>69383</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>60430</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>78874</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127570</t>
+          <t>128778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154877</t>
+          <t>155889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71279</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61422</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>80735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65494</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55127</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74690</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56287</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76597</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>47,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71279</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61788</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>80232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123419</t>
+          <t>122407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150726</t>
+          <t>149518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>140662</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140662</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>140662</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137634</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137634</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137634</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>140662</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>140662</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>140662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>61192</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52231</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>71879</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42249</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32915</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51565</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34281</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52724</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>61192</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>50806</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>70590</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>91259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117632</t>
+          <t>117673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>100903</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90216</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>109864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>115225</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>105909</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>124559</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>104750</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>123193</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>100903</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91505</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>111289</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201937</t>
+          <t>201896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229884</t>
+          <t>228310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>157474</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157474</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157474</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162095</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162095</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162095</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>261343</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>301978</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>204318</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>242337</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>205399</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>240883</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>262113</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>300282</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>474635</t>
+          <t>475291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>526569</t>
+          <t>532153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>275620</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>254633</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>295268</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>440</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>304864</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>284693</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>322712</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>286147</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>321631</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>57,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>275620</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>256329</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>294498</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>49,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>557072</t>
+          <t>551488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>609006</t>
+          <t>608350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>556611</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>556611</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>556611</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>757</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>527030</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>527030</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>527030</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>556611</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>556611</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>556611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11512</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20445</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>15434</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19854</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10804</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20217</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>45,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15938</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11690</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20324</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37509</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15856</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11349</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20282</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18232</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13812</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22793</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13449</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22862</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>54,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>67,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15856</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11470</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20104</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31794</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31794</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31794</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>33666</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>33666</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>33666</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>31794</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>31794</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>110830</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>99205</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>123926</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>74694</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62613</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84950</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>64099</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>85400</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>40,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>110830</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>99249</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>123313</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,98%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170110</t>
+          <t>169174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202651</t>
+          <t>202026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>115427</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>102331</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>127052</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>109926</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99670</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>122007</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99220</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>120521</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>59,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>115427</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>102944</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>127008</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,02%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208226</t>
+          <t>208851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240767</t>
+          <t>241703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>226257</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>226257</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>226257</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>184620</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>184620</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>184620</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>226257</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>226257</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>226257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86082</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76008</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96439</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66392</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55769</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77421</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>56101</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76450</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>86082</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75619</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>97800</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137995</t>
+          <t>136544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168035</t>
+          <t>167875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85798</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75441</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95872</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>55,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>104461</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>93432</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115084</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>94403</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114752</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85798</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74080</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>96261</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174698</t>
+          <t>174858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204738</t>
+          <t>206189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171880</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171880</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171880</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170853</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170853</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170853</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171880</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171880</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>48322</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38856</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>58353</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>33346</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24647</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42354</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>25813</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42853</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>48322</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>39250</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58784</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67341</t>
+          <t>67921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93782</t>
+          <t>93549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105681</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95650</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>115147</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>121918</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>112910</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>130617</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>112411</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>129451</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>78,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105681</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95219</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>114753</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215484</t>
+          <t>215717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241925</t>
+          <t>241345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154003</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154003</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154003</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155264</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155264</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155264</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154003</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154003</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154003</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>240456</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>281764</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>170586</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>208083</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>172831</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>207961</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>241538</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>281183</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>422726</t>
+          <t>423582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>477154</t>
+          <t>476396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>322761</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>302170</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>343478</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>354536</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>336319</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>373816</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>336441</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>371571</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,12%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>322761</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>302751</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>342396</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>651182</t>
+          <t>651940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>705610</t>
+          <t>704754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>583934</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>811</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>544402</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>544402</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>544402</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>583934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9171</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5671</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13345</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10551</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7758</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13049</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16404</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12230</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19904</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>64,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>30818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16116</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16116</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16116</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25575</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25575</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25575</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>69419</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59448</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79434</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54147</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45573</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>64067</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79687</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68781</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>57068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>133834</t>
+          <t>117400</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>104209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147842</t>
+          <t>130548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78219</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68204</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88190</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>84624</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74704</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93198</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89935</t>
+          <t>80984</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78960</t>
+          <t>71896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100841</t>
+          <t>88522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>174559</t>
+          <t>159203</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160551</t>
+          <t>146055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187546</t>
+          <t>172394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>147638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>147638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>147638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>138771</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>138771</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>138771</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>308393</t>
+          <t>276603</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>308393</t>
+          <t>276603</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>308393</t>
+          <t>276603</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75039</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86943</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>57763</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47755</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69920</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77808</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64378</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89225</t>
+          <t>67079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>131808</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120175</t>
+          <t>115981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153888</t>
+          <t>148582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>103148</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>91244</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>117174</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>104725</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>92568</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>114733</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>64,45%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107816</t>
+          <t>106545</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96399</t>
+          <t>96235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121246</t>
+          <t>117453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>212541</t>
+          <t>209692</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194224</t>
+          <t>192918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227937</t>
+          <t>225519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>178187</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>178187</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>178187</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>162488</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>162488</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>162488</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>348112</t>
+          <t>341500</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>348112</t>
+          <t>341500</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>348112</t>
+          <t>341500</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>71630</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>106746</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41921</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27434</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55375</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70745</t>
+          <t>32115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108911</t>
+          <t>52933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>132420</t>
+          <t>131179</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107207</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157984</t>
+          <t>153918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158615</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>193731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>206615</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>193161</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>221102</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>187606</t>
+          <t>185887</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169194</t>
+          <t>175038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207360</t>
+          <t>195856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>394222</t>
+          <t>362153</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>368658</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>381174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>265361</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>265361</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>265361</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>248536</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>248536</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>248536</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>278105</t>
+          <t>227971</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>278105</t>
+          <t>227971</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>278105</t>
+          <t>227971</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>526642</t>
+          <t>493332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>526642</t>
+          <t>493332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>526642</t>
+          <t>493332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214496</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>262239</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>163002</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>136345</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>185752</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155504</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>228801</t>
+          <t>139280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>279715</t>
+          <t>173325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>417604</t>
+          <t>394622</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379725</t>
+          <t>366438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453220</t>
+          <t>423257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>368183</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>345063</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>392806</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>56,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>412368</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>389618</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>439025</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>398251</t>
+          <t>389384</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373137</t>
+          <t>371563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424051</t>
+          <t>405608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>810618</t>
+          <t>757568</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775002</t>
+          <t>728933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>848497</t>
+          <t>785752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>607302</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>575370</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>575370</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>575370</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544888</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>652852</t>
+          <t>544888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1228222</t>
+          <t>1152190</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1228222</t>
+          <t>1152190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1228222</t>
+          <t>1152190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
